--- a/templates/search-ai-audit-log.xlsx
+++ b/templates/search-ai-audit-log.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Log" sheetId="1" r:id="R647cf413a6ec4784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Audit" sheetId="2" r:id="R8fd52257b4f24617"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rcfa7c618295e40d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Search Log" sheetId="1" r:id="Rdaaade8555454691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI Audit" sheetId="2" r:id="R92098145ee9e4734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="3" r:id="Rc5ac7a8bfcb14323"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -177,7 +177,7 @@
     <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1037,7 +1037,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B7" s="28" t="str">
-        <x:v>0.1 discussion draft, 2026-07-12</x:v>
+        <x:v>0.2 discussion draft, 2026-07-13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
